--- a/data/memories/memory_01/locales/es/documents/meeting_room/Meeting Attendees.xlsx
+++ b/data/memories/memory_01/locales/es/documents/meeting_room/Meeting Attendees.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meeting Attendees</t>
+          <t>Asistentes a la reunión</t>
         </is>
       </c>
     </row>
@@ -440,7 +440,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -464,41 +464,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Asistencia</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sarah K.</t>
+          <t>sara k.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Presente</t>
         </is>
       </c>
     </row>
@@ -510,46 +510,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Presente</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laura L.</t>
+          <t>laura l.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Presente</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oliver M.</t>
+          <t>óliver m.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Instalaciones</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Presente</t>
         </is>
       </c>
     </row>
@@ -561,19 +561,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ÉL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remoto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Attendance confirmed by Administration before the meeting started.</t>
+          <t>Asistencia confirmada por la Administración antes del inicio de la reunión.</t>
         </is>
       </c>
     </row>
